--- a/World_Bank_Lebanon.xlsx
+++ b/World_Bank_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2047,462 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Symposia on Supranational Responses to Corruption</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/brief/2026/11/10/integritysymposium</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>- add-style
+- lp-body-content
+3rd Symposium on Supranational Response to Corruption: Turning Illicit Gains into Development Outcomes
+Vienna, Austria
+November 9-10, 2026
+3rd Symposium Call for Contributions &amp; Background Notice
+Promoting good governance and tackling corruption are critical to achieving sustainable development and poverty reduction. The diversion of funds from development projects through corruption impairs the ability of governments, donors, and the World Bank Group (Bank Group) to achieve the goals of reducing poverty, attracting investment, and strengthening institutions. Beyond its operational and advisory work, the Bank Group plays a leading role in generating and disseminating knowledge on integrity, governance, and anti-corruption issues. By bringing together policymakers, practitioners, international organizations, academics, and other stakeholders, the Bank Group helps advance innovative approaches and shared learning to address evolving corruption risks and related development challenges.
+Recognizing the importance of collective action and knowledge exchange in the fight against corruption, the Office of Suspension and Debarment (OSD) actively promotes dialogue and collaboration across the international anti-corruption community. As part of its broader knowledge and outreach agenda, OSD leads the Symposium on Supranational Responses to Corruption series, which convenes leading experts and practitioners from across sectors to examine emerging anti-corruption challenges and institutional responses.
+The third edition of the Symposium is co-organized in partnership with the Bank Group’s Sanctions Board Secretariat, Legal Vice Presidency, and the Stolen Asset Recovery (StAR) Initiative, and with support of partners:
+- The OPEC Fund for International Development
+- Federal Ministry for European and International Affairs, Republic of Austria
+- Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ)
+- Basel Institute on Governance
+- The Chandler Foundation
+- Transparency International France
+- African Center for Governance, Asset Recovery, and Sustainable Development
+- European Law Institute
+- Civil Forum for Asset Recovery
+- Global Civil Society Coalition for the UNCAC
+- The Chinese University of Hong Kong Faculty of Law
+- Global Financial Integrity
+Note from the hosts: The World bank Group respects your privacy and is comitted to protecting it through our compliance with this Privacy Notice.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:21:55.900219+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Reforms Could Attract $1.5 Billion and Create 87,000 Jobs in Kosovo</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/press-release/2026/10/29/reforms-could-attract-1-5-billion-and-create-87-000-jobs-in-kosovo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>- add-style
+- font-medium
+- lp-body-content
+PRISTINA, October 29, 2026 - Kosovo offers important advantages for private investors, but persistent regulatory barriers continue to limit private investment and the creation of more and better-paid jobs, according to a new World Bank Group report released today.
+The Country Private Sector Diagnostic (CPSD) identifies three sub-sectors where targeted policy reforms could unlock substantial private investment: utility-scale solar and wind electricity generation, business services, and building components manufacturing. Together, reforms in these sectors could mobilize an estimated US$1.2–1.5 billion in private investment and create 61,000–87,000 direct and indirect jobs over 5-10 years.
+“To create jobs, generate domestic revenue, and foster sustainable and inclusive growth, Kosovo needs to seize untapped private investment opportunities and remove the barriers that stand in the way. The report helps Kosovo prioritize the most impactful actions to boost private sector growth while advancing broader development goals.” says Carole Megevand, World Bank Group Country Manager for Kosovo and North Macedonia.
+Kosovo aims to increase renewable sources of energy to 63 percent of installed electricity generation capacity by 2031, from just 23 percent in 2024. This requires greater certainty for investors, particularly about who will buy their electricity. Priority actions include adopting a multi-year auction schedule and operationalizing liquidity guarantees for transmission system operator KOSTT under the country’s 2025 Rule on the Renewable Energy Support Mechanism. By 2035, these reforms could mobilize $1 billion in private investment, create 8,300 jobs, and cut emissions equivalent to an estimated 24 percent of Kosovo’s annual CO2 output.
+Kosovo’s business services sector has expanded rapidly over the past decade, driven by rising European demand for outsourcing and digital services, digitalization, and cost-quality advantages. Employing a young workforce and offering comparatively high wages, the sector is a strong catalyst for the creation of better-paid jobs and possesses still untapped potential. However, growth is currently constrained by labor regulations, skills shortages, regulatory barriers, and unreliable electricity. Even narrowly targeted changes could bring significant results.
+Policy reforms, such as specifying requirements for remote and hybrid work contracts, mandating a standardized labor inspection checklist, and enabling legal recognition of e-signatures for private commercial contracts, could improve competitiveness, support expansion, and attract additional private investment. Implementation of the report’s recommendations in this sector could attract $68 $177 million in new investment and generate 32,000 to 46,000 jobs.
+Kosovo’s building components manufacturing sector is equally well-positioned to capitalize on strong domestic construction demand, on rising European appetite for energy-efficient building products, and on an established but underused export base. But policy-induced distortions and market failures raise operating costs, discourage investment, and limit firms’ ability to scale. Key constraints include unreliable and costly access to electricity, opaque land markets and cumbersome construction permitting, skills mismatches, limited access to working capital, and weak enforcement of product standards.
+Addressing these barriers could mobilize $187–$296 million in private investment and create 21,000–33,000 jobs, while strengthening export competitiveness and deepening integration between manufacturing and Kosovo’s construction sector.
+Recommended reforms include establishing a standardized long-term infrastructure use right agreement; establishing a fast-track mechanism for processing industrial construction permits submitted by manufacturing firms; requiring a structured on-the-job training module for Vocational Education and Training certification in building components manufacturing occupations; and introducing targeted, risk-based inspections of manufactured products.
+The World Bank Group remains committed to supporting Kosovo with knowledge, financing, and expertise to expand private investment, create quality jobs, and build a more prosperous future.
+Lundrim Aliu
+Filip Kochan
+World Bank Group Media Relations
+About the World Bank Group’s Activities in Kosovo
+The World Bank Group’s engagement in Kosovo dates to 1999, when the institution joined international efforts to support Kosovo’s reconstruction and recovery and opened a field office in the country. Kosovo became a full member of the World Bank Group with representation on its governing Board and full access to financing and services in June 2009. The Country Partnership Framework (CPF) for Kosovo for FY2023-2027 aims to support the country in accelerating its competitiveness for higher job creation and living standards. It outlines priorities for the World Bank Group’s engagement in the country, which are contributing to greater public service efficiency and quality, more formal private sector jobs, and increased environmental resilience.
+- add-style</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:21:58.143262+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Global Fund and World Bank Partner to Expand Access to Lifesaving Health Products</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/statement/2026/10/29/global-fund-and-world-bank-partner-to-expand-access-to-lifesaving-health-products</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>- add-style
+- lp-body-content
+Joint statement by Peter Sands, Executive Director, the Global Fund to Fight AIDS, Tuberculosis and Malaria, and Paschal Donohoe, Managing Director and Chief Knowledge Officer, World Bank Group
+The Global Fund to Fight AIDS, Tuberculosis and Malaria (the Global Fund) and the World Bank Group signed a Letter of Intent yesterday that will enable countries to use World Bank financing to buy quality-assured health products through wambo.org, the Global Fund’s online pooled procurement platform.
+The agreement builds on a Memorandum of Understanding signed by the two institutions in December 2025 to mobilize at least US$2 billion in aligned financing over three years and improve access to quality-assured health products. It also marks a further step in expanding access to wambo.org beyond Global Fund grants. The Global Fund first introduced non-Global Fund-financed procurement in 2017, and its Board mainstreamed the mechanism in 2022. In July 2026, the Board approved a new policy to expand its use, helping countries transition toward greater self-reliance while sustaining access to affordable, quality-assured health products.
+As resources become increasingly constrained and countries take on a greater share of the financing of their health programs, they need procurement solutions that offer competitive prices, quality assurance, and dependable supply. This collaboration responds directly to that need. Use of the platform will be a choice made by each country, adding a procurement option alongside national procurement systems and other existing channels.
+Pooled procurement combines orders from many buyers to obtain better prices and more reliable delivery from quality-assured suppliers. Each additional buyer increases the pooled volume, providing opportunities for improved prices and supply security for all users. In 2025, the Global Fund managed about US$1.2 billion in procurement, including more than US$1 billion through its pooled mechanism for programs in more than 80 countries. World Bank borrowers will be able to place orders through a streamlined process that meets the World Bank’s fiduciary requirements.
+Pressure on health budgets is greatest in the poorest countries. Many of them receive financing from the International Development Association (IDA), the World Bank’s fund for the poorest and the single largest source of concessional finance for the poorest countries in the world. Using IDA financing to procure from the wambo.org platform will help them get more health products for their money, and financing from the International Bank for Reconstruction and Development (IBRD) will offer the same option to middle-income countries.
+The World Bank already enables borrowers to procure through United Nations agencies. The collaboration with the Global Fund expands this approach by giving borrowers an additional procurement channel. The two institutions share a commitment to make their financing work together, reduce duplication, and ensure the multilateral system delivers more for countries. This work also contributes to the World Bank Group’s goal of helping countries deliver quality, affordable health services to 1.5 billion people by 2030.
+“As countries take the lead in financing their health programs, they should be able to buy lifesaving medicines at the best possible price and quality, whatever the source of funds,” said Peter Sands, Executive Director of the Global Fund. “By working together, the Global Fund and the World Bank can help every dollar of country financing go further.”
+"Behind every health budget are patients waiting for medicines that must arrive on time," said Paschal Donohoe, Managing Director and Chief Knowledge Officer of the World Bank Group. "Efficient procurement makes that possible, with lower prices, dependable supply, and faster delivery. Using World Bank financing in this way means more mothers, children, and families get the care they need, and brings us closer to our goal of reaching 1.5 billion people with quality, affordable health services by 2030."</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:21:59.778086+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Water Returns to Cameroon’s Bénoué Valley, Bringing New Hope for Farmers</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/feature/2026/10/26/water-returns-cameroon-benoue-valley-bringing-new-hope-for-farmers</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>- font-medium
+- bg_blue_05
+Story Highlights
+- New irrigation is bringing water back to northern Cameroon, helping farmers grow more rice, while creating jobs and building local expertise.
+- Through the VIVA Bénoué Project, lined canals and buried concrete pipes are being built on both banks of the Bénoué to bring water to farmers' fields, and a completed embankment protects about 9,500 people from floods.
+- Cameroon is among the first countries to prepare a national compact under AgriConnect, the World Bank Group initiative that aims to reach 300 million farmers by 2030, helping them improve productivity, access finance and technology, and connect to markets.
+- lp-body-content
+- first-letter
+At 65 years old, Mama Witissida, has grown rice at Gounougou in northern Cameroon since 1988. In the early years, on a scheme built by the regional agency Mission d'Études pour l'Aménagement et le Développement de la Région du Nord (MEADEN), her harvests reached seven tonnes a hectare. Then the scheme aged, water stopped arriving when the rice needed it, and yields fell, even in the fertile Bénoué Valley
+In July 2026, water released from the Lagdo Reservoir filled the newly lined main canal and reached the rehabilitated 212-hectare irrigated area at Gounougou, on the right bank of the Bénoué. For farmers like Mama, it was the first season in years with water on schedule. “Seeing water flow again gives us hope. We believe we can achieve good harvests again, provide food for our families, and sell our produce in markets here and beyond,” she says.
+It was also an important milestone for the World Bank Group-supported VIVA Bénoué Project, which is helping Cameroon make better use of its water resources, increase agricultural production, and create jobs in the country's north.
+- lp-body-content
+- first-letter
+- lp-body-content
+Getting more water to farmers
+The Lagdo Dam holds a major water reserve, but delivering that water efficiently to farms has been a longstanding challenge.
+In northern Cameroon, temperatures frequently exceed 38 degrees Celsius, and dry-season humidity can fall below 20 percent. In traditional open canals, an estimated 30 to 40 percent of water can be lost through seepage and evaporation before reaching farmers' fields.
+VIVA Bénoué is addressing this in two ways. On the right bank, it is rehabilitating and extending the gravity scheme with lined canals, starting with Gounougou. On the left bank, it is laying a new network of buried, pressurized concrete pipelines, manufactured on site at Lagdo, that cut water losses to a minimum. The completed embankment dike on the left bank also protects about 9,500 people from Bénoué floods.
+Rice is a priority. Cameroon imports large quantities of rice despite having the land and water to grow more. In Gounougou, farmers are already testing new varieties that will make the difference.
+Tchikilabi Thomas has been farming for almost 35 years. “Before the project, production was low,” he says. “Now we have a very good rice variety that gives eight to nine tonnes a hectare. We tested and validated it ourselves in the farmer field schools.”
+Building skills and creating jobs
+The project is also bringing new technical skills to the region.
+Cameroonian operators, quality-control technicians, and production engineers were trained to manufacture the specialized concrete pipes used in the irrigation network. Their experience will also serve future irrigation investments elsewhere in the country.
+On the farms, six Water Users Associations, with 484 members, including 119 women, are being trained in water scheduling, maintenance, and fee collection.
+The Ministry of Agriculture has also deployed 24 agricultural advisors, equipped with motorcycles, to work directly with farmers as the new irrigation areas become operational. An electronic voucher platform helps producers access subsidized seeds and fertilizers.
+The goal is to ensure that the investment continues to serve farmers well beyond the construction phase, with local workers and organizations taking responsibility for its operation and maintenance.
+- lp-body-content
+- first-letter
+- lp-body-content
+Connecting local investments to AgriConnect
+The work in the Bénoué Valley is part of Cameroon's wider effort to modernize agriculture and create more jobs in the agrifood sector.
+Cameroon is among the first countries to prepare a national compact under AgriConnect, the World Bank Group initiative that aims to reach 300 million smallholder and family farmers by 2030, helping them improve productivity, access finance and technology, and connect to markets.
+The country's Cameroon Country Compact at a Glance sets out priorities for expanding agricultural production and investment, including irrigation, mechanization, improved livestock genetics, digital advisory services, and cold-chain infrastructure.
+The Compact also places a strong emphasis on employment. Cameroon aims to reduce rural underemployment from 63.5 percent to 50 percent by 2030, while increasing domestic food production and reducing its food import bill.
+With the perimeter back under irrigation, the planting season brings work. Plot holders hire seasonal labor for transplanting and harvest. Fida Rosalie, a mother of five, farms half a hectare in the perimeter with her husband and takes on seasonal transplanting work. “The project is a source of income not only for the farmers, but for traders, laborers and many others,” she says.
+The rice transplanted this season will be harvested at the end of the year, the project's first measured harvest.
+For Mama Witissida, the priority is a good harvest, enough to feed her family and sell at the market. After decades in the valley, she has reasons to hope that reliable water will make that possible more often.
+Related
+- lp-body-content
+- first-letter</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:22:01.565750+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026 - Climate Finance Update</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/factsheet/2026/10/28/2026-climate-finance-update</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>- add-style
+- lp-body-content
+The World Bank Group delivered $48 billion in own-account climate co-benefits in Fiscal Year 2026, representing 44% of total commitments.
+The World Bank Group also mobilized a record $48 billion in private capital with climate co-benefits, bringing total climate-related financing to $96 billion, 21% higher than FY25.
+IFC and MIGA climate-related mobilization increased by approximately 50% from FY25, helping drive record levels of climate-related financing.
+In FY26, $15 billion in climate co-benefits supported adaptation, representing 31% of World Bank Group climate co-benefits. In IDA countries, 51% of climate co-benefits supported adaptation.
+The World Bank Group remains the largest MDB provider of climate finance to low- and middle-income countries, accounting for 50% of total MDB climate finance and 53% of adaptation finance between 2021 and 2025.
+The World Bank Group is increasingly focused not only on financing climate-smart development, but also on measuring the outcomes and impact those investments deliver for people, jobs, resilience, and growth.
+The World Bank Group’s active portfolio is expected to help 465 million people become more resilient to climate risks, a 45% increase over FY25. It is also expected to contribute to 345 million metric tons of CO₂ equivalent in net emissions reductions per year, a 13% increase over FY25.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:22:03.239719+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Expanding Legal Identity Can Unlock Services and Economic Opportunities for Millions of Haitians</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/press-release/2026/10/28/expanding-legal-identity-can-unlock-services-and-economic-opportunities-for-millio</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>- add-style
+- font-medium
+- lp-body-content
+WASHINGTON, D.C., OCTOBER 27, 2025—Haiti has an opportunity to build on recent gains in identification and extend the benefits of a valid Unique National Identification Card to more people, according to a new World Bank Group report issued today, Diagnostic of ID Ecosystems: Haiti. An estimated 2.7 to 3.1 million Haitian adults—about one in three—still need a valid card. Expanding coverage can help more people access essential services, jobs and economic opportunities.
+“Improving the ID system so that public and private service providers can use it will enable key identity verification and authentication services, such as verification of uniqueness, authenticity of credentials, and validation of identity information”, said Anne Lucie Lefebvre, World Bank Group Country manager for Haiti. “Investing in the ID ecosystem is not only a matter of fulfilling a basic right, but also a strategic opportunity to foster inclusive and sustainable access to jobs in Haiti”.
+Over recent decades, Haiti has made meaningful progress. Unique National Identification Cards have been issued to about 67 percent of adults. Among children under five, 85 percent have had their births registered and 77 percent hold a birth certificate. The 2020 Decree introducing biometric, chip-enabled ID cards, together with efforts to decentralize card printing and expand service points, demonstrates the Government’s commitment to reform. These advances provide a strong foundation for reaching poorer and rural households.
+Further progress will depend on predictable financing, clearer institutional mandates and a unified, costed national strategy. Targeted action can extend coverage to the poorest 40 percent of households, residents of remote or insecure areas, women who face cultural barriers to declaring births, and people displaced by insecurity, including deportees and internally displaced people.
+Bringing services closer to rural and insecure communities would make access easier and more affordable. Although credentials are officially free, reducing informal fees, travel costs, repeat visits and lost income would help more people enroll. Streamlining late birth registration, supporting single mothers who declare births, shortening waits, ensuring adequate materials and strengthening accountability can further build public trust.
+“Without valid ID or civil registration, people struggle to enroll in school, receive social assistance, open bank or mobile money accounts, find formal employment, and take part in civic and political life”, said Alexandre Amard, Digital specialist at the World Bank Group, co-author of the report. “Weak ID systems also make social protection programs less efficient, while keeping low-income households out of the digital economy. The lack of links between civil registration, ID and statistics data prevents reliable population estimates to guide policy”.
+Closing the remaining gaps will advance Sustainable Development Goal Target 16.9, which calls for legal identity for all, including birth registration. The diagnostic offers a practical reform agenda under three pillars: inclusion, system design and governance. Key recommendations include expanding credentials and coverage by decentralizing services, improving enrollment through mass campaigns, securing long-term financing, and modernizing laws and policy by clarifying the legal framework, adopting data protection and cybersecurity laws, and setting out a shared national vision.
+“Haiti’s identity system offers a strong foundation to build on,” the diagnostic concludes. With sustained commitment and coordinated implementation, these reforms can help all Haitians exercise their rights and gain greater access to services, social protection, financial inclusion, civic participation and economic opportunity.
+About ID4D
+The World Bank Group’s Identification for Development (ID4D) Initiative helps countries realize the transformational potential of inclusive and trusted identification and civil registration systems. ID4D’s work is made possible by the generous support of the Gates Foundation, UK International Development, the French Government, the Norwegian Agency for Development Cooperation, and the Omidyar Network.
+Peleg Charles
+- add-style</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:22:04.891813+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>World Bank Group Debars Modern Engineers Planners and Consultants Ltd.</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/press-release/2026/10/28/world-bank-group-debars-modern-engineers-planners-and-consultants-ltd</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>- add-style
+- font-medium
+- lp-body-content
+WASHINGTON, October 28, 2026—The World Bank Group today announced the 19-month debarment with conditional release of Modern Engineers Planners and Consultants Ltd., a Bangladesh-based private limited company, for fraudulent practices under the Modern Food Storage Facilities Project in Bangladesh.
+The project was designed to increase the grain reserve available to households to meet their post-disaster needs and to improve the efficiency of grain storage in Bangladesh. According to the facts of the case, Modern Engineers Planners and Consultants Ltd. (MEPC) submitted false financial documents in the procurement and false invoices for internet expenses during the implementation of a contract. These are fraudulent practices under the Bank Group Consultant Guidelines.
+The debarment makes MEPC ineligible to participate in projects and operations financed by institutions of the Bank Group. It is part of a settlement agreement under which the company admits culpability and responsibility for the underlying sanctionable practices.
+Per the Bank Group Sanctioning Guidelines, the settlement agreement provides for a reduced period of debarment in light of the company’s cooperation and voluntary remedial actions, including internal action to address the misconduct. As a condition for release from sanction under the terms of the settlement agreement, the company commits to developing integrity compliance measures that reflect the principles set out in the Bank Group Integrity Compliance Guidelines. The company also commits to continue to fully cooperate with the Bank Group Integrity Vice Presidency.
+MEPC’s debarment qualifies for cross-debarment by other multilateral development banks (MDBs) under the Agreement for Mutual Enforcement of Debarment Decisions that was signed on April 9, 2010.
+World Bank Media Relations
+- add-style</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:22:06.568949+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A Cross-Country Database of Fiscal Space</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/brief/2026/04/20/fiscal-space</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>- add-style
+- lp-body-content
+Fall 2026 version – data updated to 2025
+The World Bank’s Prospects Group has constructed a comprehensive cross-country database of fiscal space. The database covers 204 countries over the period 1990-2025, and includes 29 indicators of fiscal space grouped into four categories:
+- Government debt sustainability
+- Balance sheet composition
+- External and private sector debt
+- Market access
+The published article, written by M. Ayhan Kose, Sergio Kurlat, Franziska Ohnsorge, and Naotaka Sugawara, provides detailed information on the database and shows potential applications of the database by analyzing developments over time and during a wide range of adverse events, including financial crises, recessions, natural disasters, and wars. The working paper, originally prepared in 2017, also presents additional information and analysis related to the database.
+Data Download
+The data are available for download in Excel and Stata.
+A list of indicators with the information on sources and calculations is available in PDF.
+Citation
+When using the data, please cite the following paper as the data source:
+Kose, M. Ayhan, Sergio Kurlat, Franziska Ohnsorge, and Naotaka Sugawara. 2022. "A Cross-Country Database of Fiscal Space." Journal of International Money and Finance 128 (November): 102682.
+Disclaimer
+The concept of fiscal space used here may differ from the definition used in operational documents as defined in World Bank (2017).</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:22:08.298498+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Fiji Can Turn Economic Recovery into Stronger, More Resilient Growth: World Bank</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/press-release/2026/10/28/fiji-can-turn-economic-recovery-into-stronger-more-resilient-growth-world-bank</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>- add-style
+- font-medium
+- lp-body-content
+World Bank Group’s first Fiji Economic Update outlines how Fiji can protect households, rebuild fiscal buffers and unlock stronger, more resilient growth
+SUVA, October 26, 2026 – Fiji has made important economic progress since the pandemic, but its room to respond to future shocks is narrowing. Sustaining stronger growth will require higher productivity, stronger investment, enhanced fiscal discipline, and a broader economy according to the World Bank Group’s first Fiji Economic Update released today in Suva.
+Launched in partnership with the University of the South Pacific, the report—titled “Creating Fiscal Space to Accelerate Growth—projects the economy will grow by 2.1 percent in 2026 before recovering to 3.0 percent by 2028. Higher fuel and shipping costs are squeezing household budgets, while recent policy measures and the new external shock have begun to reverse Fiji’s earlier fiscal gains. Public debt, which fell from about 95 percent of GDP in 2021 to 76.9 percent in 2025, is projected to rise again.
+“Fiji has made real progress. Now is the time to build on it so growth supports jobs, opportunities, and a more resilient future for Fijians,” said Tatiana Proskuryakova, World Bank Group Division Director for the South and North Pacific. “Better-targeted support and careful choices about spending and revenue can protect vulnerable families while continuing to invest in infrastructure, skills and private-sector growth. Rebuilding fiscal space is about giving Fiji more choices to invest in its people while remaining able to respond to the next shock.”
+The report identifies opportunities to unlock stronger and more resilient growth by diversifying Fiji’s export base, expanding renewable energy, and strengthening agriculture and fisheries value chains alongside stronger private investment. Addressing skills shortages and increasing women’s participation in the workforce could further strengthen Fiji’s growth potential by making full use of its productive potential.
+The report finds that targeting assistance to vulnerable households can provide more effective support than broad-based relief, while making better use of limited public resources. It recommends a practical approach: target support to those who need it most, improve the quality of public spending, stabilize debt and protect investments that support growth and jobs. Stronger social protection and disaster financing can also help Fiji prepare for future shocks.
+Fiji’s Vision 2050 ambition to achieve high-income status will require a more ambitious growth rate, roughly doubling the historical growth rates from 2-3 percent to 4-6 percent. The report finds that this will require higher productivity, a more diverse economy, greater investment in people and skills, and higher workforce participation.
+Vika Waradi
+World Bank Media Relations
+- add-style</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:22:09.996128+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fiji Economic Update – October 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/brief/2026/10/28/fiji-economic-update-october-2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>col-xs-12
+col-sm-12
+col-md-1
+col-lg-1
+col-xs-12
+col-sm-12
+col-md-8
+col-lg-8
+col-xs-12
+col-sm-12
+col-md-3
+col-lg-3
+col-xs-12
+col-sm-12
+col-md-1
+col-lg-1
+col-xs-12
+col-sm-12
+col-md-7
+col-lg-7
+- add-style
+- lp-body-content
+Default alt
+eager
+Default alt
+eager
+The World Bank Group’s first Fiji Economic Update looks at how Fiji can build on its economic recovery to deliver stronger, more resilient growth, while rebuilding the fiscal space needed to respond to future shocks.
+The report highlights opportunities to strengthen growth through higher productivity, stronger investment and a broader economy, while protecting vulnerable households, improving the quality of public spending and rebuilding fiscal buffers.
+Default alt
+eager
+col-xs-12
+col-sm-12
+col-md-1
+col-lg-1
+col-xs-12
+col-sm-12
+col-md-3
+col-lg-3
+Related Content
+lp-heading-bottom-large</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:22:11.663617+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/World_Bank_Lebanon.xlsx
+++ b/World_Bank_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2503,6 +2503,308 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sri Lanka Launches AgriConnect Joint Implementation Plan to Transform Agriculture, Create Jobs</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/press-release/2026/10/29/sri-lanka-launches-agriconnect-joint-implementation-plan-to-transform-agriculture</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>col-xs-12
+col-sm-12
+col-md-1
+col-lg-1
+col-xs-12
+col-sm-12
+col-md-8
+col-lg-8
+col-xs-12
+col-sm-12
+col-md-3
+col-lg-3
+col-xs-12
+col-sm-12
+col-md-1
+col-lg-1
+col-xs-12
+col-sm-12
+col-md-7
+col-lg-7
+- add-style
+- font-medium
+- lp-body-content
+COLOMBO, October 30, 2026– The Government of Sri Lanka, in partnership with the World Bank Group and the International Fund for Agricultural Development (IFAD), today announced the launch of the Sri Lanka AgriConnect Joint Implementation Plan, a coordinated effort to transform the country’s agrifood sector, create jobs, and strengthen food security.
+true
+expert-quote, expert-quote-slider
+Sri Lanka is committed to transforming our agrifood sector from one that primarily produces commodities to one that creates greater value, better jobs and stronger opportunities for rural communities. Our farmers, fishers and rural communities are not simply beneficiaries of development, they are partners in building a stronger, more productive and more resilient economy. The AgriConnect Joint Implementation Plan will directly catalyze Government action under our Public Investment Programme, helping us connect farmers to finance, technology and markets while creating better jobs, attracting private investment and expanding opportunities across rural Sri Lanka.
+Prime Minister of Sri Lanka
+Dr. Harini Amarasuriya
+false
+Aligned with the Government’s national development agenda and Public Investment Programme 2026–2030, as well as the World Bank Group’s Country Partnership Framework, the plan brings together the Government of Sri Lanka, the World Bank Group, IFAD, development partners, financial institutions, agribusinesses, and farmers around a shared vision for a more productive, climate-resilient and market-oriented food sector.
+The initiative will help 900,000 farmers gain better access to agricultural value chains by 2030. This will be backed by $550 million in World Bank Group investments and $115 million from IFAD, and help mobilize up to $170 million in private capital over the next five years.
+Agriculture and food processing account for at least 15% of Sri Lanka’s GDP, 30% of goods exports and one in three jobs.
+true
+expert-quote, expert-quote-slider
+Sri Lanka has globally competitive agricultural products and strong entrepreneurial potential. The priority now is to connect farmers and agribusinesses with the finance, technology and markets they need to scale. By aligning public and private investment – from innovative financing to risk-sharing solutions – AgriConnect can unlock capital, strengthen agribusinesses and create more and better jobs.
+IFC Regional Vice President for Asia and the Pacific
+Sarvesh Suri
+false
+As the first country in South Asia to officially join AgriConnect, Sri Lanka will help build partnerships between farmers and agribusinesses, and advance agriculture finance, digital agriculture and AgTech, alongside cold chains, connectivity, climate-resilient irrigation, skills and research.
+The initiative will focus on value chains with strong potential for value addition and exports, including coconut, cinnamon, tea, fisheries, as well as dairy, poultry, aquaculture and horticulture. It will also support greater economic opportunities in lagging regions, including the Northern and Eastern Provinces.
+AgriConnect will also strengthen coordination among government, development partners and the private sector to tackle policy barriers, address financing constraints and unlock opportunities at scale.
+true
+expert-quote, expert-quote-slider
+There is a real opportunity to build on the progress already made in Sri Lanka’s rural economy and ensure that investments continue to reach smallholder farmers. Through AgriConnect, we can maintain this momentum and bring together the scale, financing and expertise of all partners to invest in the first mile of food systems. This means translating our shared vision into tangible realities for rural transformation: driving capital into rural areas, generating jobs, and building resilience against future shocks
+IFAD Associate Vice-President, Department for Country Operations
+Donal Brown
+false
+AgriConnect implementation has already started through the Integrated Rurban Development and Climate Resilience Project (IRDCRP) financed by the International Development Association (IDA), which connects commercially-viable businesses led by smallholder farmers to better financing and more lucrative markets through productive partnerships. IFC, a member of the World Bank Group focused on the private sector, is complementing these efforts by supporting the competitiveness and export potential of Sri Lanka’s cinnamon and coconut industries and expanding access to finance for agribusinesses through direct investments and financial-sector risk-sharing facilities.
+About AgriConnect
+AgriConnect is a World Bank Group initiative to transform farming for 300 million smallholders by 2030. It is supported by partners such as the African Development Bank (AfDB), the Inter-American Development Bank (IDB), the International Fund for Agricultural Development (IFAD), Google and Bayer.
+Contacts
+Buddhi Feelixge
+bfeelixge@worldbankgroup.org
+In Colombo
+Savani Jayasooriya
+sjayasooriya@worldbankgroup.org
+In Colombo
+about-world-bank-i18n-key
+about-world-bank
+about-world-bank-description-i18n-key
+about-world-bank-description
+col-xs-12
+col-sm-12
+col-md-1
+col-lg-1
+col-xs-12
+col-sm-12
+col-md-3
+col-lg-3
+- add-style
+Related Content
+ombc-i18n-key
+ombc
+ombc-description-i18n-key
+ombc-description
+signup-i18n-key
+signup
+register-i18n-key
+register
+everything
+true
+{"facets":[],"orderby":"contentDate desc","select":"*","searchFields":"*","search":"*","filter":"contentType eq 'Press Release'","top":20,"skip":0}
+3
+no
+yes
+no
+whats_news</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:41:43.503367+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>The Bangkok Blueprint for Fraud-Resilient Financial Services</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/brief/2026/10/29/bangkok-blueprint-for-fraud-resilient-financial-services</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>- add-style
+- lp-body-content
+Overview
+Rising cyber-enabled fraud and potential operational and cyber vulnerabilities across increasingly interconnected digital ecosystems threaten safe and inclusive digital financial services. Cyber-enabled fraud spans both unauthorized transactions, where funds move without the customer’s consent, and, increasingly, authorized transactions, where victims are manipulated into initiating transactions themselves.
+As scams become more sophisticated and industrialized, large-scale operations—often linked to transnational organized crime—are now generating losses significant enough to affect households and businesses and potentially undermine trust in the financial system, a foundation for both inclusion and stability. These threats can erode confidence in digital financial systems and services, dampening the development gains—financial inclusion, resilience, job creation, and economic growth—that they are meant to deliver.
+Since the 2018 IMF–WBG Bali Fintech Agenda, which established policy considerations for harnessing digital financial services while managing the risks, the digitalization of finance has increased innovation and efficiency while broadening access to financial services. At the same time, it has expanded the scale, speed, and sophistication with which fraud can be perpetrated. As a result, cyber-enabled fraud in financial services has emerged as a systemic policy challenge rather than a series of isolated criminal acts, requiring coordinated action across the financial sector and beyond.
+To safeguard trust in the financial system and support financial inclusion, consumer protection, integrity, and stability, this paper sets out 12 key considerations (KCs) to address cyber-enabled fraud in financial services. These KCs are intended as a high-level blueprint with a focus on the financial sector—titled the Bangkok Blueprint, and launched during the 2026 IMF–World Bank Group Annual Meetings in Thailand—to guide national policymakers, regulators, financial institutions, financial infrastructures, and other stakeholders in identifying vulnerabilities and in designing and implementing comprehensive mitigation approaches.
+The Blueprint emphasizes the need for clear strategies, fit-for-purpose legal, regulatory, and supervisory frameworks, and strong cooperation and coordination arrangements to ensure swift action. Effective fraud mitigation is ideally embedded in financial services and supported by real-time intelligence, operational capacity, and adequately protected and empowered consumers while maintaining a balance between innovation, inclusion, and risk. Its distinctive contribution is to frame cyber-enabled fraud as a financial sector policy challenge organized around five pillars: establish strategic and legal foundations; strengthen the fraud-mitigation life cycle; leverage existing risk mitigation and enforcement frameworks; expand domestic and cross-border cooperation; and promote consumer protection and resilience.
+Because fraud frequently originates outside the financial sector—on social media, digital platforms, e-commerce sites, and telecommunications networks—financial sector measures are necessary but not sufficient, and effective mitigation requires a whole-of-ecosystem response. This entails strong coordination and accountability across public sector actors, including central banks, supervisory authorities, data protection authorities, finance ministries, financial intelligence units, law enforcement, and relevant sectoral authorities, as well as with private stakeholders such as financial institutions, financial infrastructures, telecommunications providers, and digital platforms.
+In applying the KCs, national authorities are encouraged to tailor their approach to domestic conditions. Such an approach acknowledges differences in institutional, legal, and regulatory frameworks, the risk profile of cyber-enabled fraud, and the structure of digital financial ecosystems across jurisdictions. The KCs are all important and mutually reinforcing, and are not presented in order of priority. In practice, however, countries may wish to begin by conducting a risks and gaps assessment and establishing a national strategy and the necessary legal and institutional foundations, which provide the basis for sequencing the remaining measures.
+The blueprint is a nonprescriptive framework, not formal IMF and World Bank Group policy guidance. It offers considerations to address cyber-enabled fraud and aims to provide a foundation for further international engagement to ensure safe and inclusive digital finance. In developing the framework, the IMF and World Bank Group built on the work of standard-setting bodies, members’ emerging practices, and engagements with private sector stakeholders. Within their respective mandates, the Blueprint will also help IMF and World Bank Group staff develop their work on cyber-enabled fraud, inform their dialogue with national authorities, and shape their contributions to standard-setting bodies and other relevant international institutions.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:41:45.134097+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Seychelles: Creating More and Better-paid Jobs for a Prosperous Future</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/feature/2026/10/29/seychelles-creating-more-and-better-paid-jobs-for-a-prosperous-future</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>- font-medium
+- bg_blue_05
+- lp-body-content
+- first-letter
+Seychelles, a nation of 122,000 people spread across islands in the Indian Ocean, is Africa's only high-income country. Its remoteness, small size and exposure to shocks keep production and transport costs high, and the economy still leans heavily on tourism and fisheries.
+The World Bank's Seychelles Country Growth and Jobs Report 2026finds that raising productivity is the key to the next stage of growth. The reforms outlined in the report could make gross domestic product (GDP) 13% higher by 2040 than it would be without them.
+- lp-body-content
+- first-letter
+- lp-body-content
+Modernize, Utilize, Digitalize: Growth and Jobs by 2040
+Seychelles' growth record is getting harder to sustain. Its population is aging and employers struggle to find skilled workers, while firms and households have been slow to adopt digital tools. The report sets out three priorities that work best together: modernize the labor market and business rules, fully utilize Seychellois talent, and digitalize the economy.
+- By 2040, the three priorities together could bring more than 10,000 new and better-paid jobs: 2,900 new jobs and the equivalent of more than 7,600 better-paid ones, compared to a no-reform scenario.
+- Real wages could be almost 8% higher and labor productivity 8.3% higher.
+- Household consumption per person could rise by 8.1%.
+- lp-body-content
+- first-letter
+- lp-body-content
+Foreign Workers, Work Permits and Competitiveness
+As the population ages, Seychelles will need better-trained Seychellois to do higher-paid jobs. But the economy will also continue to need foreign workers. Foreign workers currently hold 39% of private sector jobs, mostly high-wage and minimum-wage ones, so they complement Seychellois workers rather than compete with them. Hiring them is slow, and the delays hurt firms' competitiveness. The report recommends investing in young people's skills to get more Seychellois into work and better-paid jobs, while also introducing a faster, online, and more flexible work permit system for foreign workers, alongside measures to ease pressure on housing and helping foreign workers integrate.
+- People over 65 made up 9% of the population in 2017 and are projected to reach 26% by 2050.
+- The working-age population is expected to stay at about 55,000 over the next 15 years.
+- It took 20 weeks, on average, to get a Gainful Occupation Permit in 2024, compared with 4 to 6 weeks in Mauritius and around 3 weeks in the Maldives.
+- lp-body-content
+- first-letter
+- lp-body-content
+Skills and Jobs for Young People
+Better jobs and wider use of new technology depend on the skills of young Seychellois. Four problems hold many of them back: disengagement from school, substance abuse, teenage pregnancy and a weak link between school and work. About one in five people aged 15 to 24 is not in education, employment or training. The report calls for a prevention-first approach centered on schools, with action on learning, job-relevant skills training, access to health services and early support for young people at risk.
+- In 2022, only 9% of Secondary 3 students, at around age 14, met the expected standard in mathematics, and 43% in English.
+- By 2040, these reforms could create 687 new jobs and the equivalent of 490 better-paid jobs.
+- lp-body-content
+- first-letter
+- lp-body-content
+- lp-body-content
+- first-letter</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:41:46.898312+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Nigeria: Investing in Childcare for Women’s Jobs</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/feature/2026/10/29/nigeria-childcare-market-womens-jobs</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>- font-medium
+- bg_blue_05
+Story Highlights
+- Only 5 percent of Nigeria’s private sector employers invest in childcare, while women spend up to six hours a day on unpaid care work. Closing the gender gap in key sectors of the economy could yield up to $23 billion, or 6 percent of GDP.
+- The World Bank Group is helping Nigeria build a more accessible, professional childcare market by strengthening care standards, and helping women-led businesses access finance.
+- Over 4,500 aspiring caregivers and entrepreneurs—about 90 percent of them women—are training toward national childcare standards.
+- lp-body-content
+- first-letter
+Nonye Afagwu spent years working as a nurse in a school, caring for other people’s children while knowing, as any parent does, how hard it is to find someone you trust to care for your own. When she attended a “Women, Jobs, and Markets in Nigeria” Evidence Forum, organized by the World Bank Group in April 2025, it dawned on her that childcare could also be a business opportunity. By September 2025, Nonye had set up her own childcare center.
+“Just from that convening,” says Adaorie Udechukwu, International Finance Corporation’s (IFC) Program Lead behind the Care Works program in Nigeria, “we birthed one job that’s going to hire more women. Imagine the ripple effect when we train thousands.”
+In Nigeria, only five percent of private sector employers invest in childcare and women spend up to six hours a day on unpaid care work. The World Bank Group is addressing these interconnected constraints by building a more accessible, professional, and investible childcare market.
+Nigeria’s challenge is part of a global one. Around the world, an estimated 708 million women, compared with 40 million men, are out of the workforce because of care responsibilities. At the same time, nearly 350 million children below primary school age need childcare but do not have access to it.
+The numbers make the case. In 2022, the World Bank estimated that closing the gender gap in key sectors of Nigeria’s economy could yield an economic gain of as much as $23 billion, or 6 percent of Nigeria’s overall GDP. Yet 76 percent of childcare entrepreneurs lack access to formal finance, and 92 percent of facilities are small, independently owned, and invisible to banks.
+The childcare market is broken on multiple sides: entrepreneurs cannot get loans, parents cannot afford quality care, and workers lack credentials to prove their skills. Fixing one side in isolation does not work, which is why the initiative in Nigeria is, by design, a coordinated effort across the World Bank Group.
+Nigeria is one of the countries where the World Bank Group is intentionally bringing public and private sector solutions together to advance gender equality as part of its 2024-2030 Gender Strategy. A grant from the Umbrella Facility for Gender Equality (UFGE), a multi donor trust fund, provided the seed funding for teams to analyze what could do the most for women in Nigeria. Childcare topped the list.
+The resulting IDEAS Project, supported by the World Bank, developed Nigeria’s first-ever National Occupational Standards for childcare, a baseline that had never existed before. Over 4,500 aspiring caregivers and entrepreneurs—about 90 percent of them women—are currently training towards those standards.
+- lp-body-content
+- first-letter
+- lp-body-content
+On the private sector side, the International Finance Corporation (IFC) is working to draw commercial banks and institutional investors directly into the sector through IFC’s Invest in Care platform. Its Care Business Accelerator also works with women-led enterprises to make them ready to borrow, connecting them to financial institutions and to employers through a peer-learning platform called Allies4Care. Finally, the project team is exploring ways to encourage banks and financial institutions to invest in care at scale.
+Coordinating across the public and private sectors creates a pipeline. A woman gets trained and certified. She can work in a certified facility or start one. The facility can access finance. Employers begin to see childcare as a business investment, not a welfare cost. And evidence from the Nigeria Gender Innovation Lab, a World Bank research unit, tests what works, so the models can scale.
+Behind these efforts is a larger ambition to show that childcare is an investible sector, its workforce a professional one, and its returns in women’s employment, child development, and GDP real and measurable. The global evidence shows the way. Every dollar invested in closing childcare gaps could yield $3.76 in global GDP by 2035. What’s more, investing in care services and policies could create 300 million new decent jobs by 2035, most of them benefiting women. (Read UN Women’s policy brief on building care systems)
+“The question is not whether care matters, but how governments can design policies and investments that reduce the economic costs of unpaid care and expand opportunities for women and families,” says Robin Mearns, Global Director for Gender at the World Bank Group.
+Nonye Afagwu’s childcare center is an early example of the broader impact the initiative seeks to generate through thousands of trained caregivers and the jobs their skills and enterprises can create.
+- lp-body-content
+- first-letter</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:41:48.583385+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa’s Growing Cities Offer Path to Millions of New Jobs</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/press-release/2026/10/29/sub-saharan-africa-urban-awakening</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>- add-style
+- font-medium
+- lp-body-content
+New World Bank Group report sets out priorities to turn the region’s rapid urbanization into more productive cities and better jobs
+WASHINGTON, October 29, 2026—Sub-Saharan Africa’s cities could become powerful engines of economic growth and job creation if governments focus investments and policy attention on places where firms can form clusters and workers can easily reach them, according to a new World Bank Group report.
+The newly-released Sub-Saharan Africa’s Urban Awakening: Catalyzing Economic Growth and Job Creation report projects that the region will add 748 million urban residents between 2025 and 2050. It finds that this growth offers a time-bound opportunity to create more and better jobs for the region’s expanding young workforce. Cities already offer stronger prospects: urban households spend considerably more per adult than equally educated rural households, reflecting more and better jobs.
+The report finds that realizing this potential will require targeted action to address the different challenges facing cities, their rapidly growing peripheries, and smaller towns. In major cities, governments should prioritize the fostering of accessible, job-rich clusters by investing in infrastructure, transport and well-located affordable housing, while improving regulations that enable firms and workers to locate closer to economic opportunities. On city peripheries, governments need to plan ahead for rapid expansion, particularly by establishing road networks and reserving space for essential infrastructure before development becomes entrenched.
+The report also highlights the often-overlooked potential of Sub-Saharan Africa’s more than 15,000 towns. For smaller towns, the report recommends a selective approach to investment, focusing resources on places with strong economic and geographic potential, particularly towns along transport corridors and near other economic opportunities.
+In these high-potential towns, targeted infrastructure and stronger urban planning can help unlock growth and job creation, while investment in education and health can help residents in towns with fewer economic opportunities connect to stronger labor markets. The report also calls for rapidly growing towns to have the appropriate urban governance and financing tools they need to better plan for future expansion.
+The report recommends practical, cost-effective measures, such as using low-cost technology to modernize property tax systems that can raise local revenue, improve city creditworthiness, and help attract private investment, including through public-private partnerships in key city locations.
+With Sub-Saharan Africa’s urban future taking shape now, the choices made today will shape the region’s cities for generations to come. The report emphasizes the need to act early and strategically, combining targeted infrastructure investments with stronger institutions, better urban planning and financing, and greater mobilization of private capital. Together, these measures can help ensure the region’s rapid urban growth translates into greater economic opportunity and more and better jobs.
+World Bank Group Media Relations
+- add-style</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:41:50.270625+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/World_Bank_Lebanon.xlsx
+++ b/World_Bank_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2805,6 +2805,130 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RISE +</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/feature/2026/10/30/rise</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>- lp-body-content
+- first-letter
+Transaction-oriented support to critical mineral value chains in developing countries
+RISE Plus (RISE+) is a dedicated pillar established in September 2026 under the PHRD Technical Assistance Program to translate upstream policy, data, and institutional work in critical minerals value chains into transaction-oriented support from the World Bank Group. It aims to help countries move from reform and investment pipeline identification toward bankable investments, while supporting high-quality job creation, local value addition, and more diversified value chains. RISE+ will also be implemented by the International Finance Corporation (IFC) through the Comprehensive Japan Trust Fund (CJTF).
+The facility is designed to complement the existing Resilient and Inclusive Supply Chain Enhancement Partnership (RISE) initiative, managed by the World Bank’s Extractives Global Programmatic Support (EGPS) Trust Fund. RISE will continue to support upstream policy dialogue, sector reform, analytical work, public-sector capacity building, and investment facilitation. RISE+ will focus on the transaction support needed to convert those reforms, frameworks, and investment roadmaps into bankable opportunities.
+RISE+ will support activities that help emerging markets and developing economies prepare, structure, and advance priority investments across critical minerals value chains. While the facility may support activities across the value chain, particular emphasis will be placed on midstream and downstream opportunities, including processing, refining, and enabling infrastructure, where investment preparation and risk mitigation can help unlock private capital.
+RISE+ is aligned with Japan’s commitment to resilient, diversified, and inclusive supply chains and with the World Bank Group’s engagement on minerals and metals as a driver of sustainable development, investment mobilization, and local value creation.
+- lp-body-content
+- first-letter</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-31T11:12:45.276365+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Pakistan: New World Bank Program to Strengthen Municipal Revenues and Services in Sindh</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/news/press-release/2026/10/30/pakistan-new-world-bank-program-to-strengthen-municipal-revenues-and-services-in-s</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>- add-style
+- font-medium
+- lp-body-content
+WASHINGTON, October 30, 2026 - The World Bank Group’s Board of Executive Directors today approved US$150 million in financing for the Sindh Property Revenues Enhancement Program (Sindh PREP). The program will improve urban property tax collection and strengthen municipal service delivery in Sindh.
+"Cities that can raise their own revenues can plan and invest for the long term," saidBolormaa Amgaabazar, World Bank Country Director for Pakistan. "Today, Sindh's local councils depend on provincial transfers for more than 95 percent of their revenues. By helping Karachi collect the property taxes from its residents and businesses, and by reinvesting most of that revenue in local services, this program will give Sindh's cities the means to finance the infrastructure they need.”
+The Sindh Property Revenues Enhancement Program (Sindh PREP) will support the Government of Sindh in improving urban immovable property tax (UIPT) collection and strengthening municipal service delivery capacity in selected local councils of Sindh. Despite being one of the world's largest cities, Karachi currently collects only approximately US$8.5 million annually in property tax while cities of similar size collect 82 to 350 times more. The program aims to increase this to US$85 million annually - raising compliance from 20 to 50 percent. It will do so by strengthening UIPT collection, compliance, and administration, including through deployment of a UIPT management information system for billing, payment processing, and grievance redress, and by rolling out integrated financial management information systems across local councils. About 70 percent of collected UIPT revenues will be reinvested directly into municipal infrastructure and services in participating local councils.
+The program will benefit Karachi's 25 local councils. Its primary beneficiaries are the 3.58 million people living in these councils, where service delivery investments will be financed. Funding will be linked to results: annual performance assessments, conducted by an Independent Verification Agent, will determine the awards each council receives, and these awards will finance the rehabilitation of climate-resilient municipal infrastructure and services, including drainage, sewerage, schools, fire stations, roads, and street lighting. The program also includes an Investment Project Financing component of US$40 million that will expand property surveys and UIPT administration to 20 local councils in Sindh's other urban centers, with an indirect benefit to approximately 4.5 million people.
+"Karachi has significant untapped potential to generate revenues from its property base and use those resources to fund the infrastructure its residents and businesses need. This program will help Sindh strengthen fiscal sustainability enabling cities to plan, invest, and deliver services from their own resources effectively," saidDavison Muchadenyika, Senior Urban Development Specialist at the World Bank.
+The World Bank Group in Pakistan
+Pakistan has been a member of the World Bank since 1950. Since then, the World Bank has provided a total of US$52 billion in assistance. The current portfolio has 47 operations, including one regional project, with a total commitment of approximately US$16.1 billion.
+IFC has invested and mobilized approximately US$22 billion in Pakistan since 1959, with a diverse range of projects supporting renewable energy, financial inclusion, infrastructure development, agribusiness, manufacturing, housing, healthcare, and trade, among others. IFC’s committed portfolio stood at US$1.6 billion across 55 projects as of September 30, 2026.
+For more information, read the Pakistan Country Partnership Framework 2026-35 document
+Mariam Sara Altaf
+Serene Jweied
+- add-style</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-31T11:12:46.910367+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Human Capital Ministerial Conclave: Private Capital for Skills in the Age of AI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/brief/2026/10/29/human-capital-ministerial-conclave-private-capital-for-skills-in-the-age-of-ai</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>- add-style
+- lp-body-content
+100+ economies share approaches to skills, jobs, and working with the private sector to advance human capital
+Over the next decade, 1.2 billion young people in emerging economies will enter the workforce, many into jobs that AI is already reshaping. Yet nearly 7 in 10 children in low- and middle-income countries cannot read a simple text by age 10, leaving too many without the foundation needed to thrive.
+The stakes are high. Whether people benefit from new technologies will depend on whether countries invest now in the health, education, and skills people need to use them.
+That challenge shaped the 2026 Human Capital Ministerial Conclave, held during the World Bank Group and IMF Annual Meetings in Bangkok. Representatives from 42 Human Capital Project member countries joined development partners and private-sector experts to explore how AI can widen opportunities and how private investment and expertise can help equip people for jobs.
+The case for acting is simple. Health, education, and skills are among the highest-return investments a government can make. Between one-third and two-thirds of the difference in income per person across countries comes down to human capital.
+Foundational learning is critical
+Speakers stressed that AI cannot replace the basics. A child who cannot read with understanding will struggle to make sense of what AI tells them. “AI is the technology. Learning is the outcome,” said Catherine Russell, Executive Director, UNICEF. AI can help teachers spot struggling students and reach children with disabilities. It cannot replace teachers.
+Sandeep Aneja, Founder and Managing Partner, Kaizenvest, said young people also need to build what AI cannot replace: creativity, perseverance, and judgment.
+What private capital can bring
+“Governments and policymakers create markets. Private capital shapes the markets,” Sandeep Aneja said. Investors bring risk-taking and innovations that scale quickly, but they need clear frameworks from governments.
+One commitment, different approaches
+Sixteen government representatives described a shared commitment to investing in people, pursued through different combinations of public funding, private investment, incentives, and technology.
+Approaches included wage subsidies that cover part of the cost of hiring young people, with many placements leading to longer-term contracts; national plans that set aside significant funding for education and skills and expect the private sector to finance a large share; and tax incentives that draw private investment into education.
+Other countries are using AI and digital platforms to overcome distance and limited scale. Examples include using AI to bring quality teaching to every island in an archipelago, shared regional digital training platforms for small island states, national programs to train young people and civil servants in AI, and AI tutors and coaches being tested in secondary schools with World Bank Group support.
+Countries also emphasized the enabling conditions for responsible AI adoption. Ministers shared that AI only helps if connectivity and digital infrastructure come first and if AI governance frameworks protect people without stifling innovation. People must be equipped to advance with advances in technology.
+A growing network
+The Conclave also marked a milestone: Botswana, Gabon, Kosovo, Mauritius, Thailand, and Zimbabwe joined the Human Capital Project this year. The network has grown from 28 member economies in 2018 to 102 today. Through data, dialogue, and country diagnostics, it helps ministries learn from approaches that work elsewhere and adapt them to local contexts.
+The new members join the Human Capital Project with ambitions to advance human capital at home. Some are creating national bodies that bring government, industry, and education leaders together to align learning with labor-market needs. Others see a young population as an advantage only if young people finish school with the skills their economies need, stay healthy, and find good jobs at home.
+The private sector as a partner in a changing world of work
+Mamta Murthi, World Bank Group Vice President for People, closed the Conclave with a clear takeaway: the private sector is a key partner in financing skills and workforce development and in bringing innovation that improves the outcomes of public spending. She encouraged countries to continue learning from one another and to join the Conclave again in 2027.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-31T11:12:48.544775+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
